--- a/data/lillestrom_monitoring_sites.xlsx
+++ b/data/lillestrom_monitoring_sites.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JES\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{134BFA3F-0D7A-48C7-8922-A968B86A9E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F400A1-ED43-4068-AD30-3F9674D0A125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{9C3A7A90-CD7A-4778-99B7-8FCC1DE9F218}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{9C3A7A90-CD7A-4778-99B7-8FCC1DE9F218}"/>
   </bookViews>
   <sheets>
     <sheet name="catch_outlets" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">catch_outlets!$A$1:$G$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">chem_stns!$A$1:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">chem_stns!$A$1:$I$14</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="83">
   <si>
     <t>station_id</t>
   </si>
@@ -287,6 +287,12 @@
   </si>
   <si>
     <t>Rud Nitelva (N8)</t>
+  </si>
+  <si>
+    <t>002-30575</t>
+  </si>
+  <si>
+    <t>Frogner Leira</t>
   </si>
 </sst>
 </file>
@@ -902,7 +908,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4880EC8-8A50-4537-94A7-456C2129CA91}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
@@ -1120,89 +1126,89 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F8" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="G8" s="2">
-        <v>11.22099</v>
+        <v>11.097950000000001</v>
       </c>
       <c r="H8" s="2">
-        <v>60.021630000000002</v>
+        <v>60.022849999999998</v>
       </c>
       <c r="I8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G9" s="2">
-        <v>11.10637</v>
+        <v>11.22099</v>
       </c>
       <c r="H9" s="2">
-        <v>60.001989999999999</v>
+        <v>60.021630000000002</v>
       </c>
       <c r="I9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G10" s="2">
-        <v>11.300179999999999</v>
+        <v>11.10637</v>
       </c>
       <c r="H10" s="2">
-        <v>59.992089999999997</v>
+        <v>60.001989999999999</v>
       </c>
       <c r="I10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1210,28 +1216,28 @@
         <v>67</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
         <v>53</v>
       </c>
       <c r="E11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="G11" s="2">
-        <v>11.34807</v>
+        <v>11.300179999999999</v>
       </c>
       <c r="H11" s="2">
-        <v>59.985120000000002</v>
+        <v>59.992089999999997</v>
       </c>
       <c r="I11" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -1239,61 +1245,90 @@
         <v>67</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
         <v>53</v>
       </c>
       <c r="E12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" s="2">
+        <v>11.34807</v>
+      </c>
+      <c r="H12" s="2">
+        <v>59.985120000000002</v>
+      </c>
+      <c r="I12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" t="s">
         <v>56</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F13" t="s">
         <v>57</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G13" s="2">
         <v>11.348229999999999</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H13" s="2">
         <v>59.983910000000002</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I13" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>32</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C14" t="s">
         <v>33</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D14" t="s">
         <v>60</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E14" t="s">
         <v>58</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F14" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G14" s="2">
         <v>11.22275</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H14" s="2">
         <v>59.86139</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I14" t="s">
         <v>64</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I13" xr:uid="{F4880EC8-8A50-4537-94A7-456C2129CA91}"/>
+  <autoFilter ref="A1:I14" xr:uid="{F4880EC8-8A50-4537-94A7-456C2129CA91}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
